--- a/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD_DP_PYRAD/rwd-only/results.xlsx
+++ b/mlef_pipeline/results/OS_6/HIGH_PDL1/RWD_DP_PYRAD/rwd-only/results.xlsx
@@ -468,22 +468,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.43 ± 0.12</t>
+          <t>0.67 ± 0.13</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.25 ± 0.07</t>
+          <t>0.30 ± 0.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.32 ± 0.47</t>
+          <t>0.38 ± 0.45</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.68 ± 0.47</t>
+          <t>0.59 ± 0.43</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -498,17 +498,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.79 ± 0.13</t>
+          <t>0.95 ± 0.08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -528,17 +528,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.75 ± nan</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
